--- a/Attainment Calculation/22-23 PIC 22226 Barate Batch/CR3_22226 PIC Barate Batch Filled Sheet/CR3_22226 - Programming in _C_.xlsx
+++ b/Attainment Calculation/22-23 PIC 22226 Barate Batch/CR3_22226 PIC Barate Batch Filled Sheet/CR3_22226 - Programming in _C_.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSBTE-28\Documents\ada\gpd_nba\Attainment Calculation\22-23 PIC 22226 Barate Batch\CR3_22226 PIC Barate Batch Filled Sheet\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1703725D-CBF9-4DCB-A735-ADC7F8B1E16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PO Set Target attain level" sheetId="1" r:id="rId1"/>
@@ -48,12 +42,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{3F5F1909-F23F-4E2D-82A3-CE076689DC62}">
+    <comment ref="D12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1085,11 +1079,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1439,6 +1433,13 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -3247,6 +3248,23 @@
     <xf numFmtId="0" fontId="57" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3269,85 +3287,25 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="45" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="47" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3392,17 +3350,54 @@
     <xf numFmtId="0" fontId="47" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3449,11 +3444,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3480,20 +3474,15 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3514,11 +3503,41 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3539,40 +3558,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3596,25 +3600,22 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3649,7 +3650,7 @@
         <xdr:cNvPr id="3" name="Shape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3713,7 +3714,7 @@
         <xdr:cNvPr id="4" name="Shape 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3777,7 +3778,7 @@
         <xdr:cNvPr id="2" name="Shape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3841,7 +3842,7 @@
         <xdr:cNvPr id="5" name="Shape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3905,7 +3906,7 @@
         <xdr:cNvPr id="6" name="Shape 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3974,7 +3975,7 @@
         <xdr:cNvPr id="5" name="Shape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4045,7 +4046,7 @@
         <xdr:cNvPr id="6" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4102,11 +4103,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PO Set Target attain level"/>
       <sheetName val="CO_Attainment for Unit Tests"/>
@@ -4355,7 +4353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -4392,10 +4390,10 @@
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="238" t="s">
+      <c r="D3" s="222" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="232"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:13">
@@ -4404,10 +4402,10 @@
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="238">
+      <c r="D4" s="222">
         <v>22226</v>
       </c>
-      <c r="E4" s="232"/>
+      <c r="E4" s="223"/>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:13">
@@ -4416,10 +4414,10 @@
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="238" t="s">
+      <c r="D5" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="232"/>
+      <c r="E5" s="223"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:13">
@@ -4428,10 +4426,10 @@
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="238" t="s">
+      <c r="D6" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="232"/>
+      <c r="E6" s="223"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75">
@@ -4557,31 +4555,31 @@
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:25">
-      <c r="B17" s="227" t="s">
+      <c r="B17" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="227" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="233" t="s">
+      <c r="D17" s="228"/>
+      <c r="E17" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="234"/>
-      <c r="L17" s="233" t="s">
+      <c r="F17" s="225"/>
+      <c r="G17" s="225"/>
+      <c r="H17" s="225"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="225"/>
+      <c r="K17" s="226"/>
+      <c r="L17" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="M17" s="234"/>
+      <c r="M17" s="226"/>
     </row>
     <row r="18" spans="1:25">
-      <c r="B18" s="228"/>
-      <c r="C18" s="241"/>
-      <c r="D18" s="242"/>
+      <c r="B18" s="239"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="230"/>
       <c r="E18" s="19" t="s">
         <v>27</v>
       </c>
@@ -4611,9 +4609,9 @@
       </c>
     </row>
     <row r="19" spans="1:25" ht="122.25" customHeight="1">
-      <c r="B19" s="229"/>
-      <c r="C19" s="243"/>
-      <c r="D19" s="244"/>
+      <c r="B19" s="240"/>
+      <c r="C19" s="231"/>
+      <c r="D19" s="232"/>
       <c r="E19" s="20" t="s">
         <v>36</v>
       </c>
@@ -4883,11 +4881,11 @@
       </c>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1">
-      <c r="B26" s="235" t="s">
+      <c r="B26" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="236"/>
-      <c r="D26" s="234"/>
+      <c r="C26" s="225"/>
+      <c r="D26" s="226"/>
       <c r="E26" s="22">
         <f t="shared" ref="E26:M26" si="6">IFERROR(AVERAGE(E20:E24),2)</f>
         <v>3</v>
@@ -4926,11 +4924,11 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1">
-      <c r="B27" s="237" t="s">
+      <c r="B27" s="244" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="236"/>
-      <c r="D27" s="234"/>
+      <c r="C27" s="225"/>
+      <c r="D27" s="226"/>
       <c r="E27" s="27">
         <f t="shared" ref="E27:M27" si="7">E26</f>
         <v>3</v>
@@ -4974,32 +4972,32 @@
       <c r="D30" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="230" t="s">
+      <c r="I30" s="241" t="s">
         <v>49</v>
       </c>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="225"/>
+      <c r="J30" s="236"/>
+      <c r="K30" s="236"/>
+      <c r="L30" s="236"/>
+      <c r="M30" s="236"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1">
       <c r="A31" s="30"/>
       <c r="B31" s="30"/>
-      <c r="C31" s="231" t="s">
+      <c r="C31" s="242" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="232"/>
-      <c r="E31" s="232"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
-      <c r="I31" s="231" t="s">
+      <c r="I31" s="242" t="s">
         <v>50</v>
       </c>
-      <c r="J31" s="232"/>
-      <c r="K31" s="232"/>
-      <c r="L31" s="232"/>
-      <c r="M31" s="232"/>
+      <c r="J31" s="223"/>
+      <c r="K31" s="223"/>
+      <c r="L31" s="223"/>
+      <c r="M31" s="223"/>
       <c r="N31" s="30"/>
       <c r="O31" s="30"/>
       <c r="P31" s="30"/>
@@ -5017,22 +5015,22 @@
     <row r="33" spans="2:5" ht="15.75" customHeight="1"/>
     <row r="34" spans="2:5" ht="15.75" customHeight="1"/>
     <row r="35" spans="2:5" ht="28.5" customHeight="1">
-      <c r="B35" s="222" t="s">
+      <c r="B35" s="233" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="31"/>
-      <c r="D35" s="224" t="s">
+      <c r="D35" s="235" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="225"/>
+      <c r="E35" s="236"/>
     </row>
     <row r="36" spans="2:5" ht="47.25" customHeight="1">
-      <c r="B36" s="223"/>
+      <c r="B36" s="234"/>
       <c r="C36" s="27"/>
-      <c r="D36" s="226" t="s">
+      <c r="D36" s="237" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="225"/>
+      <c r="E36" s="236"/>
     </row>
     <row r="37" spans="2:5" ht="15.75" customHeight="1"/>
     <row r="38" spans="2:5" ht="15.75" customHeight="1"/>
@@ -6002,12 +6000,6 @@
     <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="E17:K17"/>
-    <mergeCell ref="C17:D19"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
@@ -6018,6 +6010,12 @@
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="E17:K17"/>
+    <mergeCell ref="C17:D19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="69" orientation="landscape"/>
@@ -6026,7 +6024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9267,7 +9265,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -9295,35 +9293,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.75">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="254" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
       <c r="L1" s="180"/>
     </row>
     <row r="2" spans="1:12" ht="21.75">
-      <c r="A2" s="277" t="s">
+      <c r="A2" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="225"/>
-      <c r="C2" s="225"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
       <c r="L2" s="180"/>
     </row>
     <row r="3" spans="1:12">
@@ -9331,11 +9329,11 @@
       <c r="B3" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="278" t="str">
+      <c r="C3" s="255" t="str">
         <f>'[1]PO Set Target attain level'!D3</f>
         <v>Programming in _C_</v>
       </c>
-      <c r="D3" s="279"/>
+      <c r="D3" s="256"/>
       <c r="E3" s="180"/>
       <c r="F3" s="180"/>
       <c r="G3" s="180"/>
@@ -9350,11 +9348,11 @@
       <c r="B4" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="278">
+      <c r="C4" s="255">
         <f>'[1]PO Set Target attain level'!D4</f>
         <v>22226</v>
       </c>
-      <c r="D4" s="279"/>
+      <c r="D4" s="256"/>
       <c r="E4" s="180"/>
       <c r="F4" s="180"/>
       <c r="G4" s="180"/>
@@ -9369,11 +9367,11 @@
       <c r="B5" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="278" t="str">
+      <c r="C5" s="255" t="str">
         <f>'[1]PO Set Target attain level'!D5</f>
         <v>2nd SEM(CO2I SCHEME)</v>
       </c>
-      <c r="D5" s="279"/>
+      <c r="D5" s="256"/>
       <c r="E5" s="180"/>
       <c r="F5" s="180"/>
       <c r="G5" s="180"/>
@@ -9388,11 +9386,11 @@
       <c r="B6" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="278" t="str">
+      <c r="C6" s="255" t="str">
         <f>'[1]PO Set Target attain level'!D6</f>
         <v>2022 - 23</v>
       </c>
-      <c r="D6" s="279"/>
+      <c r="D6" s="256"/>
       <c r="E6" s="180"/>
       <c r="F6" s="180"/>
       <c r="G6" s="180"/>
@@ -9417,31 +9415,31 @@
       <c r="L7" s="180"/>
     </row>
     <row r="8" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A8" s="280" t="s">
+      <c r="A8" s="257" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="289" t="s">
+      <c r="B8" s="266" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="290" t="s">
+      <c r="C8" s="267" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="291" t="s">
+      <c r="D8" s="268" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="292" t="s">
+      <c r="E8" s="269" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="287" t="s">
+      <c r="F8" s="264" t="s">
         <v>271</v>
       </c>
-      <c r="G8" s="288" t="s">
+      <c r="G8" s="265" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="273" t="s">
+      <c r="H8" s="250" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="276" t="s">
+      <c r="I8" s="253" t="s">
         <v>64</v>
       </c>
       <c r="J8" s="183" t="s">
@@ -9453,53 +9451,53 @@
       <c r="L8" s="180"/>
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A9" s="274"/>
-      <c r="B9" s="274"/>
-      <c r="C9" s="274"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="274"/>
-      <c r="I9" s="274"/>
-      <c r="J9" s="281" t="s">
+      <c r="A9" s="251"/>
+      <c r="B9" s="251"/>
+      <c r="C9" s="251"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="258" t="s">
         <v>67</v>
       </c>
-      <c r="K9" s="282"/>
+      <c r="K9" s="259"/>
       <c r="L9" s="180"/>
     </row>
     <row r="10" spans="1:12" ht="23.25" customHeight="1">
-      <c r="A10" s="274"/>
-      <c r="B10" s="274"/>
-      <c r="C10" s="274"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="274"/>
-      <c r="F10" s="274"/>
-      <c r="G10" s="274"/>
-      <c r="H10" s="274"/>
-      <c r="I10" s="274"/>
-      <c r="J10" s="283"/>
-      <c r="K10" s="284"/>
+      <c r="A10" s="251"/>
+      <c r="B10" s="251"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="261"/>
       <c r="L10" s="180"/>
     </row>
     <row r="11" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A11" s="274"/>
-      <c r="B11" s="274"/>
-      <c r="C11" s="274"/>
-      <c r="D11" s="275"/>
-      <c r="E11" s="275"/>
-      <c r="F11" s="275"/>
-      <c r="G11" s="275"/>
-      <c r="H11" s="275"/>
-      <c r="I11" s="275"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="286"/>
+      <c r="A11" s="251"/>
+      <c r="B11" s="251"/>
+      <c r="C11" s="251"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="263"/>
       <c r="L11" s="180"/>
     </row>
     <row r="12" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A12" s="275"/>
-      <c r="B12" s="275"/>
-      <c r="C12" s="275"/>
+      <c r="A12" s="252"/>
+      <c r="B12" s="252"/>
+      <c r="C12" s="252"/>
       <c r="D12" s="184">
         <v>12</v>
       </c>
@@ -12589,101 +12587,101 @@
       <c r="L94" s="180"/>
     </row>
     <row r="95" spans="1:12" ht="60.75" customHeight="1">
-      <c r="A95" s="245" t="s">
+      <c r="A95" s="293" t="s">
         <v>137</v>
       </c>
-      <c r="B95" s="225"/>
+      <c r="B95" s="236"/>
       <c r="C95" s="206">
         <v>0.4</v>
       </c>
-      <c r="D95" s="246">
+      <c r="D95" s="245">
         <f t="shared" ref="D95:I95" si="4">$C$95*D12</f>
         <v>4.8000000000000007</v>
       </c>
-      <c r="E95" s="246">
+      <c r="E95" s="245">
         <f t="shared" si="4"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="F95" s="246">
+      <c r="F95" s="245">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="G95" s="246">
+      <c r="G95" s="245">
         <f t="shared" si="4"/>
         <v>3.2</v>
       </c>
-      <c r="H95" s="246">
+      <c r="H95" s="245">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I95" s="246">
+      <c r="I95" s="245">
         <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
-      <c r="J95" s="293"/>
-      <c r="K95" s="293"/>
+      <c r="J95" s="247"/>
+      <c r="K95" s="247"/>
       <c r="L95" s="180"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A96" s="248" t="s">
+      <c r="A96" s="294" t="s">
         <v>138</v>
       </c>
-      <c r="B96" s="225"/>
-      <c r="C96" s="249"/>
-      <c r="D96" s="247"/>
-      <c r="E96" s="247"/>
-      <c r="F96" s="247"/>
-      <c r="G96" s="247"/>
-      <c r="H96" s="247"/>
-      <c r="I96" s="247"/>
-      <c r="J96" s="247"/>
-      <c r="K96" s="247"/>
+      <c r="B96" s="236"/>
+      <c r="C96" s="286"/>
+      <c r="D96" s="246"/>
+      <c r="E96" s="246"/>
+      <c r="F96" s="246"/>
+      <c r="G96" s="246"/>
+      <c r="H96" s="246"/>
+      <c r="I96" s="246"/>
+      <c r="J96" s="246"/>
+      <c r="K96" s="246"/>
       <c r="L96" s="180"/>
     </row>
     <row r="97" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A97" s="225"/>
-      <c r="B97" s="225"/>
-      <c r="C97" s="249"/>
-      <c r="D97" s="250">
+      <c r="A97" s="236"/>
+      <c r="B97" s="236"/>
+      <c r="C97" s="286"/>
+      <c r="D97" s="249">
         <f t="shared" ref="D97:I97" si="5">COUNTIF(D13:D94,"&gt;=" &amp;D95)</f>
         <v>52</v>
       </c>
-      <c r="E97" s="250">
+      <c r="E97" s="249">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="F97" s="250">
+      <c r="F97" s="249">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="G97" s="250">
+      <c r="G97" s="249">
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="H97" s="250">
+      <c r="H97" s="249">
         <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="I97" s="250">
+      <c r="I97" s="249">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="J97" s="294"/>
-      <c r="K97" s="294"/>
+      <c r="J97" s="248"/>
+      <c r="K97" s="248"/>
       <c r="L97" s="180"/>
     </row>
     <row r="98" spans="1:12" ht="15.75" customHeight="1">
       <c r="A98" s="180"/>
       <c r="B98" s="180"/>
       <c r="C98" s="180"/>
-      <c r="D98" s="247"/>
-      <c r="E98" s="247"/>
-      <c r="F98" s="247"/>
-      <c r="G98" s="247"/>
-      <c r="H98" s="247"/>
-      <c r="I98" s="247"/>
-      <c r="J98" s="247"/>
-      <c r="K98" s="247"/>
+      <c r="D98" s="246"/>
+      <c r="E98" s="246"/>
+      <c r="F98" s="246"/>
+      <c r="G98" s="246"/>
+      <c r="H98" s="246"/>
+      <c r="I98" s="246"/>
+      <c r="J98" s="246"/>
+      <c r="K98" s="246"/>
       <c r="L98" s="180"/>
     </row>
     <row r="99" spans="1:12" ht="15.75" customHeight="1">
@@ -12730,94 +12728,94 @@
     </row>
     <row r="102" spans="1:12" ht="43.5" customHeight="1">
       <c r="A102" s="180"/>
-      <c r="B102" s="257" t="s">
+      <c r="B102" s="276" t="s">
         <v>139</v>
       </c>
-      <c r="C102" s="252"/>
-      <c r="D102" s="252"/>
-      <c r="E102" s="258"/>
-      <c r="F102" s="259" t="s">
+      <c r="C102" s="271"/>
+      <c r="D102" s="271"/>
+      <c r="E102" s="277"/>
+      <c r="F102" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G102" s="258"/>
+      <c r="G102" s="277"/>
       <c r="H102" s="207"/>
-      <c r="I102" s="260" t="s">
+      <c r="I102" s="279" t="s">
         <v>141</v>
       </c>
-      <c r="J102" s="258"/>
+      <c r="J102" s="277"/>
       <c r="K102" s="180"/>
       <c r="L102" s="180"/>
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1">
       <c r="A103" s="180"/>
-      <c r="B103" s="261" t="s">
+      <c r="B103" s="280" t="s">
         <v>142</v>
       </c>
-      <c r="C103" s="251" t="s">
+      <c r="C103" s="270" t="s">
         <v>143</v>
       </c>
-      <c r="D103" s="252"/>
+      <c r="D103" s="271"/>
       <c r="E103" s="208">
         <v>50</v>
       </c>
-      <c r="F103" s="264">
+      <c r="F103" s="283">
         <v>69</v>
       </c>
-      <c r="G103" s="265"/>
+      <c r="G103" s="284"/>
       <c r="H103" s="209">
         <f>E103*F103/100</f>
         <v>34.5</v>
       </c>
-      <c r="I103" s="269">
+      <c r="I103" s="289">
         <v>1</v>
       </c>
-      <c r="J103" s="270"/>
+      <c r="J103" s="290"/>
       <c r="K103" s="180"/>
       <c r="L103" s="180"/>
     </row>
     <row r="104" spans="1:12" ht="15.75" customHeight="1">
       <c r="A104" s="180"/>
-      <c r="B104" s="262"/>
-      <c r="C104" s="251" t="s">
+      <c r="B104" s="281"/>
+      <c r="C104" s="270" t="s">
         <v>144</v>
       </c>
-      <c r="D104" s="252"/>
+      <c r="D104" s="271"/>
       <c r="E104" s="208">
         <v>60</v>
       </c>
-      <c r="F104" s="266"/>
-      <c r="G104" s="249"/>
+      <c r="F104" s="285"/>
+      <c r="G104" s="286"/>
       <c r="H104" s="210">
         <f>E104*F103/100</f>
         <v>41.4</v>
       </c>
-      <c r="I104" s="271">
+      <c r="I104" s="291">
         <v>2</v>
       </c>
-      <c r="J104" s="272"/>
+      <c r="J104" s="292"/>
       <c r="K104" s="180"/>
       <c r="L104" s="180"/>
     </row>
     <row r="105" spans="1:12" ht="15.75" customHeight="1">
       <c r="A105" s="180"/>
-      <c r="B105" s="263"/>
-      <c r="C105" s="251" t="s">
+      <c r="B105" s="282"/>
+      <c r="C105" s="270" t="s">
         <v>145</v>
       </c>
-      <c r="D105" s="252"/>
+      <c r="D105" s="271"/>
       <c r="E105" s="211">
         <v>70</v>
       </c>
-      <c r="F105" s="267"/>
-      <c r="G105" s="268"/>
+      <c r="F105" s="287"/>
+      <c r="G105" s="288"/>
       <c r="H105" s="212">
         <f>E105*F103/100</f>
         <v>48.3</v>
       </c>
-      <c r="I105" s="253">
+      <c r="I105" s="272">
         <v>3</v>
       </c>
-      <c r="J105" s="254"/>
+      <c r="J105" s="273"/>
       <c r="K105" s="180"/>
       <c r="L105" s="180"/>
     </row>
@@ -12829,9 +12827,9 @@
       <c r="E106" s="213"/>
       <c r="F106" s="213"/>
       <c r="G106" s="213"/>
-      <c r="H106" s="255"/>
-      <c r="I106" s="256"/>
-      <c r="J106" s="256"/>
+      <c r="H106" s="274"/>
+      <c r="I106" s="275"/>
+      <c r="J106" s="275"/>
       <c r="K106" s="180"/>
       <c r="L106" s="180"/>
     </row>
@@ -12843,9 +12841,9 @@
       <c r="E107" s="213"/>
       <c r="F107" s="213"/>
       <c r="G107" s="213"/>
-      <c r="H107" s="255"/>
-      <c r="I107" s="256"/>
-      <c r="J107" s="256"/>
+      <c r="H107" s="274"/>
+      <c r="I107" s="275"/>
+      <c r="J107" s="275"/>
       <c r="K107" s="180"/>
       <c r="L107" s="180"/>
     </row>
@@ -16548,14 +16546,29 @@
     <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="J95:J96"/>
-    <mergeCell ref="K95:K96"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="K97:K98"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="A96:C97"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="H107:J107"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:G105"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="I104:J104"/>
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="I8:I11"/>
     <mergeCell ref="A1:K1"/>
@@ -16572,29 +16585,14 @@
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="D8:D11"/>
     <mergeCell ref="E8:E11"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="H106:J106"/>
-    <mergeCell ref="H107:J107"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G105"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="I104:J104"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="A96:C97"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="J95:J96"/>
+    <mergeCell ref="K95:K96"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="K97:K98"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="I97:I98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -16603,7 +16601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -16620,13 +16618,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="20.25">
-      <c r="B1" s="295" t="s">
+      <c r="B1" s="316" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
@@ -16695,11 +16693,11 @@
       <c r="C4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="296" t="str">
+      <c r="D4" s="317" t="str">
         <f>'CO_Attainment for Unit Tests'!C3</f>
         <v>Programming in _C_</v>
       </c>
-      <c r="E4" s="232"/>
+      <c r="E4" s="223"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -16723,11 +16721,11 @@
       <c r="C5" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="296">
+      <c r="D5" s="317">
         <f>'CO_Attainment for Unit Tests'!C4</f>
         <v>22226</v>
       </c>
-      <c r="E5" s="232"/>
+      <c r="E5" s="223"/>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
@@ -16751,11 +16749,11 @@
       <c r="C6" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="296" t="str">
+      <c r="D6" s="317" t="str">
         <f>'CO_Attainment for Unit Tests'!C5</f>
         <v>2nd SEM(CO2I SCHEME)</v>
       </c>
-      <c r="E6" s="232"/>
+      <c r="E6" s="223"/>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
@@ -16779,11 +16777,11 @@
       <c r="C7" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="296" t="str">
+      <c r="D7" s="317" t="str">
         <f>'CO_Attainment for Unit Tests'!C6</f>
         <v>2022 - 23</v>
       </c>
-      <c r="E7" s="232"/>
+      <c r="E7" s="223"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -16806,43 +16804,43 @@
       <c r="E8" s="17"/>
     </row>
     <row r="9" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B9" s="311" t="s">
+      <c r="B9" s="309" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="302" t="s">
+      <c r="C9" s="300" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="299" t="s">
+      <c r="D9" s="297" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="302" t="s">
+      <c r="E9" s="300" t="s">
         <v>153</v>
       </c>
       <c r="J9" s="44"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="B10" s="300"/>
-      <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
-      <c r="E10" s="300"/>
+      <c r="B10" s="298"/>
+      <c r="C10" s="298"/>
+      <c r="D10" s="298"/>
+      <c r="E10" s="298"/>
       <c r="J10" s="45"/>
     </row>
     <row r="11" spans="2:22">
-      <c r="B11" s="300"/>
-      <c r="C11" s="300"/>
-      <c r="D11" s="300"/>
-      <c r="E11" s="300"/>
+      <c r="B11" s="298"/>
+      <c r="C11" s="298"/>
+      <c r="D11" s="298"/>
+      <c r="E11" s="298"/>
     </row>
     <row r="12" spans="2:22" ht="27.75" customHeight="1">
-      <c r="B12" s="300"/>
-      <c r="C12" s="300"/>
-      <c r="D12" s="300"/>
-      <c r="E12" s="301"/>
+      <c r="B12" s="298"/>
+      <c r="C12" s="298"/>
+      <c r="D12" s="298"/>
+      <c r="E12" s="299"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="301"/>
-      <c r="C13" s="301"/>
-      <c r="D13" s="301"/>
+      <c r="B13" s="299"/>
+      <c r="C13" s="299"/>
+      <c r="D13" s="299"/>
       <c r="E13" s="34">
         <v>70</v>
       </c>
@@ -18215,7 +18213,7 @@
       <c r="D97" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="E97" s="303">
+      <c r="E97" s="301">
         <f>D98*E13/100</f>
         <v>35.021000000000001</v>
       </c>
@@ -18224,7 +18222,7 @@
       <c r="D98" s="50">
         <v>50.03</v>
       </c>
-      <c r="E98" s="229"/>
+      <c r="E98" s="240"/>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1">
       <c r="D99" s="51" t="s">
@@ -18250,12 +18248,12 @@
       <c r="E102" s="17"/>
     </row>
     <row r="103" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A103" s="304" t="s">
+      <c r="A103" s="302" t="s">
         <v>139</v>
       </c>
-      <c r="B103" s="236"/>
-      <c r="C103" s="236"/>
-      <c r="D103" s="234"/>
+      <c r="B103" s="225"/>
+      <c r="C103" s="225"/>
+      <c r="D103" s="226"/>
       <c r="E103" s="55" t="s">
         <v>140</v>
       </c>
@@ -18267,17 +18265,17 @@
       <c r="I103" s="57"/>
     </row>
     <row r="104" spans="1:9" ht="15" customHeight="1">
-      <c r="A104" s="305" t="s">
+      <c r="A104" s="303" t="s">
         <v>142</v>
       </c>
       <c r="B104" s="58">
         <v>0.5</v>
       </c>
-      <c r="C104" s="308" t="s">
+      <c r="C104" s="306" t="s">
         <v>156</v>
       </c>
-      <c r="D104" s="309"/>
-      <c r="E104" s="310">
+      <c r="D104" s="307"/>
+      <c r="E104" s="308">
         <f>COUNTA(D14:D96)-COUNTIFS(D14:D96,0)</f>
         <v>69</v>
       </c>
@@ -18292,15 +18290,15 @@
       <c r="I104" s="57"/>
     </row>
     <row r="105" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A105" s="306"/>
+      <c r="A105" s="304"/>
       <c r="B105" s="61">
         <v>0.6</v>
       </c>
-      <c r="C105" s="312" t="s">
+      <c r="C105" s="310" t="s">
         <v>156</v>
       </c>
-      <c r="D105" s="313"/>
-      <c r="E105" s="228"/>
+      <c r="D105" s="311"/>
+      <c r="E105" s="239"/>
       <c r="F105" s="62">
         <f t="shared" si="0"/>
         <v>41.4</v>
@@ -18312,15 +18310,15 @@
       <c r="I105" s="57"/>
     </row>
     <row r="106" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A106" s="307"/>
+      <c r="A106" s="305"/>
       <c r="B106" s="64">
         <v>0.7</v>
       </c>
-      <c r="C106" s="314" t="s">
+      <c r="C106" s="312" t="s">
         <v>157</v>
       </c>
-      <c r="D106" s="315"/>
-      <c r="E106" s="229"/>
+      <c r="D106" s="313"/>
+      <c r="E106" s="240"/>
       <c r="F106" s="65">
         <f t="shared" si="0"/>
         <v>48.3</v>
@@ -18354,10 +18352,10 @@
       <c r="I108" s="57"/>
     </row>
     <row r="109" spans="1:9" ht="71.25" customHeight="1">
-      <c r="A109" s="316" t="s">
+      <c r="A109" s="314" t="s">
         <v>158</v>
       </c>
-      <c r="B109" s="317"/>
+      <c r="B109" s="315"/>
       <c r="C109" s="40" t="s">
         <v>9</v>
       </c>
@@ -18379,10 +18377,10 @@
       <c r="I109" s="57"/>
     </row>
     <row r="110" spans="1:9" ht="39" customHeight="1">
-      <c r="A110" s="297" t="s">
+      <c r="A110" s="295" t="s">
         <v>159</v>
       </c>
-      <c r="B110" s="298"/>
+      <c r="B110" s="296"/>
       <c r="C110" s="42">
         <f>IF(E99&gt;=$F106,3,IF(E99&gt;=$F105,2,IF(E99&gt;=$F104,1,0)))</f>
         <v>1</v>
@@ -19721,6 +19719,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="A110:B110"/>
     <mergeCell ref="D9:D13"/>
     <mergeCell ref="E9:E12"/>
@@ -19734,11 +19737,6 @@
     <mergeCell ref="C105:D105"/>
     <mergeCell ref="C106:D106"/>
     <mergeCell ref="A109:B109"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -19747,7 +19745,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -19795,11 +19793,11 @@
       <c r="C4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="318" t="str">
+      <c r="D4" s="329" t="str">
         <f>'CO_Attainment for Unit Tests'!C3</f>
         <v>Programming in _C_</v>
       </c>
-      <c r="E4" s="319"/>
+      <c r="E4" s="328"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -19809,11 +19807,11 @@
       <c r="C5" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="318">
+      <c r="D5" s="329">
         <f>'CO_Attainment for Unit Tests'!C4</f>
         <v>22226</v>
       </c>
-      <c r="E5" s="319"/>
+      <c r="E5" s="328"/>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
@@ -19823,11 +19821,11 @@
       <c r="C6" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="318" t="str">
+      <c r="D6" s="329" t="str">
         <f>'CO_Attainment for Unit Tests'!C5</f>
         <v>2nd SEM(CO2I SCHEME)</v>
       </c>
-      <c r="E6" s="319"/>
+      <c r="E6" s="328"/>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
@@ -19837,63 +19835,63 @@
       <c r="C7" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="318" t="str">
+      <c r="D7" s="329" t="str">
         <f>'CO_Attainment for Unit Tests'!C6</f>
         <v>2022 - 23</v>
       </c>
-      <c r="E7" s="319"/>
+      <c r="E7" s="328"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B9" s="311" t="s">
+      <c r="B9" s="309" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="302" t="s">
+      <c r="C9" s="300" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="320" t="s">
+      <c r="D9" s="330" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="322" t="s">
+      <c r="E9" s="319" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="323" t="s">
+      <c r="F9" s="320" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="324" t="s">
+      <c r="G9" s="321" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B10" s="300"/>
-      <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
-      <c r="E10" s="300"/>
-      <c r="F10" s="300"/>
-      <c r="G10" s="325"/>
+      <c r="B10" s="298"/>
+      <c r="C10" s="298"/>
+      <c r="D10" s="298"/>
+      <c r="E10" s="298"/>
+      <c r="F10" s="298"/>
+      <c r="G10" s="322"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B11" s="300"/>
-      <c r="C11" s="300"/>
-      <c r="D11" s="300"/>
-      <c r="E11" s="300"/>
-      <c r="F11" s="300"/>
-      <c r="G11" s="325"/>
+      <c r="B11" s="298"/>
+      <c r="C11" s="298"/>
+      <c r="D11" s="298"/>
+      <c r="E11" s="298"/>
+      <c r="F11" s="298"/>
+      <c r="G11" s="322"/>
     </row>
     <row r="12" spans="2:8" ht="54.75" customHeight="1">
-      <c r="B12" s="300"/>
-      <c r="C12" s="300"/>
-      <c r="D12" s="300"/>
-      <c r="E12" s="301"/>
-      <c r="F12" s="301"/>
-      <c r="G12" s="326"/>
+      <c r="B12" s="298"/>
+      <c r="C12" s="298"/>
+      <c r="D12" s="298"/>
+      <c r="E12" s="299"/>
+      <c r="F12" s="299"/>
+      <c r="G12" s="323"/>
     </row>
     <row r="13" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B13" s="301"/>
-      <c r="C13" s="301"/>
-      <c r="D13" s="301"/>
+      <c r="B13" s="299"/>
+      <c r="C13" s="299"/>
+      <c r="D13" s="299"/>
       <c r="E13" s="34">
         <v>10</v>
       </c>
@@ -21592,15 +21590,15 @@
       <c r="D97" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="E97" s="327">
+      <c r="E97" s="324">
         <f>ROUNDUP(D98*E13/100,1)</f>
         <v>6</v>
       </c>
-      <c r="F97" s="327">
+      <c r="F97" s="324">
         <f>ROUNDUP(D98*F13/100,1)</f>
         <v>15</v>
       </c>
-      <c r="G97" s="327">
+      <c r="G97" s="324">
         <f>ROUNDUP(D98*G13/100,1)</f>
         <v>15</v>
       </c>
@@ -21609,9 +21607,9 @@
       <c r="D98" s="73">
         <v>60</v>
       </c>
-      <c r="E98" s="229"/>
-      <c r="F98" s="229"/>
-      <c r="G98" s="229"/>
+      <c r="E98" s="240"/>
+      <c r="F98" s="240"/>
+      <c r="G98" s="240"/>
     </row>
     <row r="99" spans="1:8" ht="15.75" customHeight="1">
       <c r="D99" s="51" t="s">
@@ -21635,11 +21633,11 @@
     <row r="102" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="103" spans="1:8" ht="46.5" customHeight="1">
       <c r="A103" s="57"/>
-      <c r="B103" s="304" t="s">
+      <c r="B103" s="302" t="s">
         <v>168</v>
       </c>
-      <c r="C103" s="236"/>
-      <c r="D103" s="234"/>
+      <c r="C103" s="225"/>
+      <c r="D103" s="226"/>
       <c r="E103" s="74" t="s">
         <v>140</v>
       </c>
@@ -21651,7 +21649,7 @@
     </row>
     <row r="104" spans="1:8" ht="15.75" customHeight="1">
       <c r="A104" s="57"/>
-      <c r="B104" s="305" t="s">
+      <c r="B104" s="303" t="s">
         <v>142</v>
       </c>
       <c r="C104" s="58">
@@ -21660,7 +21658,7 @@
       <c r="D104" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="E104" s="310">
+      <c r="E104" s="308">
         <f>COUNTA(D14:D96)-COUNTIFS(D14:D96,0)</f>
         <v>69</v>
       </c>
@@ -21675,14 +21673,14 @@
     </row>
     <row r="105" spans="1:8" ht="15.75" customHeight="1">
       <c r="A105" s="57"/>
-      <c r="B105" s="306"/>
+      <c r="B105" s="304"/>
       <c r="C105" s="61">
         <v>0.6</v>
       </c>
       <c r="D105" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="E105" s="228"/>
+      <c r="E105" s="239"/>
       <c r="F105" s="76">
         <f>C105*$E104</f>
         <v>41.4</v>
@@ -21694,14 +21692,14 @@
     </row>
     <row r="106" spans="1:8" ht="15.75" customHeight="1">
       <c r="A106" s="57"/>
-      <c r="B106" s="307"/>
+      <c r="B106" s="305"/>
       <c r="C106" s="64">
         <v>0.7</v>
       </c>
       <c r="D106" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="E106" s="229"/>
+      <c r="E106" s="240"/>
       <c r="F106" s="77">
         <f>C106*$E104</f>
         <v>48.3</v>
@@ -21732,10 +21730,10 @@
       <c r="H108" s="57"/>
     </row>
     <row r="109" spans="1:8" ht="33" customHeight="1">
-      <c r="A109" s="233" t="s">
+      <c r="A109" s="224" t="s">
         <v>169</v>
       </c>
-      <c r="B109" s="328"/>
+      <c r="B109" s="325"/>
       <c r="C109" s="78" t="s">
         <v>9</v>
       </c>
@@ -21756,10 +21754,10 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A110" s="329" t="s">
+      <c r="A110" s="326" t="s">
         <v>170</v>
       </c>
-      <c r="B110" s="317"/>
+      <c r="B110" s="315"/>
       <c r="C110" s="80">
         <f>IF(E99&gt;=$F106,3,IF(E99&gt;=$F105,2,IF(E99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -21786,10 +21784,10 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="48.75" customHeight="1">
-      <c r="A111" s="330" t="s">
+      <c r="A111" s="327" t="s">
         <v>171</v>
       </c>
-      <c r="B111" s="319"/>
+      <c r="B111" s="328"/>
       <c r="C111" s="82">
         <f>IF(F99&gt;=$F106,3,IF(F99&gt;=$F105,2,IF(F99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -21816,10 +21814,10 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A112" s="321" t="s">
+      <c r="A112" s="318" t="s">
         <v>172</v>
       </c>
-      <c r="B112" s="298"/>
+      <c r="B112" s="296"/>
       <c r="C112" s="42">
         <f>IF(G99&gt;=$F106,3,IF(G99&gt;=$F105,2,IF(G99&gt;=$F104,1,0)))</f>
         <v>3</v>
@@ -22745,6 +22743,13 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="D9:D13"/>
     <mergeCell ref="A112:B112"/>
     <mergeCell ref="E9:E12"/>
     <mergeCell ref="F9:F12"/>
@@ -22758,13 +22763,6 @@
     <mergeCell ref="A109:B109"/>
     <mergeCell ref="A110:B110"/>
     <mergeCell ref="A111:B111"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="D9:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="28" orientation="landscape"/>
@@ -22773,7 +22771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -22866,41 +22864,41 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1">
-      <c r="B10" s="333" t="s">
+      <c r="B10" s="343" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="334" t="s">
+      <c r="C10" s="331" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="335" t="s">
+      <c r="D10" s="344" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="334" t="s">
+      <c r="E10" s="331" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="228"/>
-      <c r="C11" s="228"/>
-      <c r="D11" s="228"/>
-      <c r="E11" s="228"/>
+      <c r="B11" s="239"/>
+      <c r="C11" s="239"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
+      <c r="B12" s="239"/>
+      <c r="C12" s="239"/>
+      <c r="D12" s="239"/>
+      <c r="E12" s="239"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="228"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="336"/>
+      <c r="B13" s="239"/>
+      <c r="C13" s="239"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="332"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="229"/>
-      <c r="C14" s="229"/>
-      <c r="D14" s="229"/>
+      <c r="B14" s="240"/>
+      <c r="C14" s="240"/>
+      <c r="D14" s="240"/>
       <c r="E14" s="87">
         <v>5</v>
       </c>
@@ -23697,57 +23695,57 @@
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="85" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A85" s="337" t="s">
+      <c r="A85" s="333" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="236"/>
-      <c r="C85" s="236"/>
-      <c r="D85" s="234"/>
+      <c r="B85" s="225"/>
+      <c r="C85" s="225"/>
+      <c r="D85" s="226"/>
       <c r="E85" s="94" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A86" s="338" t="s">
+      <c r="A86" s="334" t="s">
         <v>142</v>
       </c>
-      <c r="B86" s="339" t="s">
+      <c r="B86" s="335" t="s">
         <v>182</v>
       </c>
-      <c r="C86" s="340"/>
-      <c r="D86" s="309"/>
+      <c r="C86" s="336"/>
+      <c r="D86" s="307"/>
       <c r="E86" s="95">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A87" s="306"/>
-      <c r="B87" s="341" t="s">
+      <c r="A87" s="304"/>
+      <c r="B87" s="337" t="s">
         <v>183</v>
       </c>
-      <c r="C87" s="342"/>
-      <c r="D87" s="313"/>
+      <c r="C87" s="338"/>
+      <c r="D87" s="311"/>
       <c r="E87" s="96">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A88" s="307"/>
-      <c r="B88" s="343" t="s">
+      <c r="A88" s="305"/>
+      <c r="B88" s="339" t="s">
         <v>184</v>
       </c>
-      <c r="C88" s="344"/>
-      <c r="D88" s="315"/>
+      <c r="C88" s="340"/>
+      <c r="D88" s="313"/>
       <c r="E88" s="97">
         <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="90" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A90" s="331" t="s">
+      <c r="A90" s="341" t="s">
         <v>169</v>
       </c>
-      <c r="B90" s="328"/>
+      <c r="B90" s="325"/>
       <c r="C90" s="98" t="s">
         <v>9</v>
       </c>
@@ -23765,10 +23763,10 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1">
-      <c r="A91" s="332" t="s">
+      <c r="A91" s="342" t="s">
         <v>185</v>
       </c>
-      <c r="B91" s="317"/>
+      <c r="B91" s="315"/>
       <c r="C91" s="100">
         <f>IF(E81&gt;=80,3,IF(E81&gt;=65,2,IF(E81&gt;=40,1,0)))</f>
         <v>0</v>
@@ -24710,17 +24708,17 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="D10:D14"/>
     <mergeCell ref="E10:E13"/>
     <mergeCell ref="A85:D85"/>
     <mergeCell ref="A86:A88"/>
     <mergeCell ref="B86:D86"/>
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="B88:D88"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D10:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -24728,7 +24726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -24785,34 +24783,34 @@
       <c r="P5" s="17"/>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="227" t="s">
+      <c r="B6" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="239" t="s">
+      <c r="C6" s="227" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="240"/>
-      <c r="E6" s="233" t="s">
+      <c r="D6" s="228"/>
+      <c r="E6" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="234"/>
-      <c r="O6" s="233" t="s">
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="234"/>
+      <c r="P6" s="226"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="228"/>
-      <c r="C7" s="241"/>
-      <c r="D7" s="242"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="230"/>
       <c r="E7" s="19" t="s">
         <v>27</v>
       </c>
@@ -24851,9 +24849,9 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="62.25">
-      <c r="B8" s="229"/>
-      <c r="C8" s="243"/>
-      <c r="D8" s="244"/>
+      <c r="B8" s="240"/>
+      <c r="C8" s="231"/>
+      <c r="D8" s="232"/>
       <c r="E8" s="20" t="s">
         <v>194</v>
       </c>
@@ -25177,8 +25175,8 @@
       <c r="B15" s="345" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="236"/>
-      <c r="D15" s="234"/>
+      <c r="C15" s="225"/>
+      <c r="D15" s="226"/>
       <c r="E15" s="107">
         <f t="shared" ref="E15:P15" si="0">ROUNDUP(AVERAGE(E9:E14),2)</f>
         <v>3</v>
@@ -25232,8 +25230,8 @@
       <c r="B16" s="346" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="236"/>
-      <c r="D16" s="234"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="226"/>
       <c r="E16" s="108">
         <f t="shared" ref="E16:P16" si="1">ROUNDUP((E15*2.66)/3,2)</f>
         <v>2.66</v>
@@ -25287,8 +25285,8 @@
       <c r="B17" s="346" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="236"/>
-      <c r="D17" s="234"/>
+      <c r="C17" s="225"/>
+      <c r="D17" s="226"/>
       <c r="E17" s="108">
         <f t="shared" ref="E17:P17" si="2">ROUNDUP((E16/3)*100,2)</f>
         <v>88.67</v>
@@ -26334,7 +26332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -26575,16 +26573,16 @@
     <row r="8" spans="1:26" ht="21">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
-      <c r="C8" s="347" t="s">
+      <c r="C8" s="353" t="s">
         <v>216</v>
       </c>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="234"/>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="226"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
@@ -26605,18 +26603,18 @@
     <row r="9" spans="1:26">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="348" t="s">
+      <c r="C9" s="354" t="s">
         <v>217</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="349" t="s">
+      <c r="D9" s="225"/>
+      <c r="E9" s="225"/>
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="226"/>
+      <c r="I9" s="355" t="s">
         <v>218</v>
       </c>
-      <c r="J9" s="240"/>
+      <c r="J9" s="228"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
@@ -26637,20 +26635,20 @@
     <row r="10" spans="1:26">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
-      <c r="C10" s="350" t="s">
+      <c r="C10" s="356" t="s">
         <v>219</v>
       </c>
-      <c r="D10" s="351" t="s">
+      <c r="D10" s="357" t="s">
         <v>220</v>
       </c>
-      <c r="E10" s="352"/>
-      <c r="F10" s="352"/>
-      <c r="G10" s="244"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
+      <c r="G10" s="232"/>
       <c r="H10" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="I10" s="243"/>
-      <c r="J10" s="244"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="232"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
@@ -26671,7 +26669,7 @@
     <row r="11" spans="1:26" ht="45.75" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
-      <c r="C11" s="229"/>
+      <c r="C11" s="240"/>
       <c r="D11" s="111" t="s">
         <v>222</v>
       </c>
@@ -26687,10 +26685,10 @@
       <c r="H11" s="114" t="s">
         <v>225</v>
       </c>
-      <c r="I11" s="353" t="s">
+      <c r="I11" s="359" t="s">
         <v>226</v>
       </c>
-      <c r="J11" s="234"/>
+      <c r="J11" s="226"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
@@ -26734,11 +26732,11 @@
         <f>'CO_attainment for FA-TH ESE'!C110</f>
         <v>1</v>
       </c>
-      <c r="I12" s="354">
+      <c r="I12" s="349">
         <f>'CO_attainment for Indirect'!C91</f>
         <v>0</v>
       </c>
-      <c r="J12" s="309"/>
+      <c r="J12" s="307"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -26782,11 +26780,11 @@
         <f t="shared" ref="H13:H17" si="3">$H12</f>
         <v>1</v>
       </c>
-      <c r="I13" s="358">
+      <c r="I13" s="348">
         <f t="shared" ref="I13:I17" si="4">$I12</f>
         <v>0</v>
       </c>
-      <c r="J13" s="313"/>
+      <c r="J13" s="311"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
@@ -26830,11 +26828,11 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I14" s="358">
+      <c r="I14" s="348">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J14" s="313"/>
+      <c r="J14" s="311"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
@@ -26878,11 +26876,11 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I15" s="358">
+      <c r="I15" s="348">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J15" s="313"/>
+      <c r="J15" s="311"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
@@ -26926,11 +26924,11 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I16" s="358">
+      <c r="I16" s="348">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J16" s="313"/>
+      <c r="J16" s="311"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
@@ -26974,11 +26972,11 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I17" s="358">
+      <c r="I17" s="348">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="313"/>
+      <c r="J17" s="311"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
@@ -27022,11 +27020,11 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I18" s="354">
+      <c r="I18" s="349">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J18" s="309"/>
+      <c r="J18" s="307"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
@@ -27065,10 +27063,10 @@
       <c r="H19" s="128">
         <v>60</v>
       </c>
-      <c r="I19" s="359">
+      <c r="I19" s="350">
         <v>100</v>
       </c>
-      <c r="J19" s="319"/>
+      <c r="J19" s="328"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
@@ -27112,11 +27110,11 @@
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
-      <c r="I20" s="355">
+      <c r="I20" s="351">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J20" s="315"/>
+      <c r="J20" s="313"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
@@ -27137,13 +27135,13 @@
     <row r="21" spans="1:26" ht="48" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
-      <c r="C21" s="356" t="s">
+      <c r="C21" s="352" t="s">
         <v>230</v>
       </c>
-      <c r="D21" s="236"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="236"/>
-      <c r="G21" s="234"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="226"/>
       <c r="H21" s="130">
         <f>SUM(D20:H20)</f>
         <v>1.6669999999999998</v>
@@ -27175,13 +27173,13 @@
     <row r="22" spans="1:26" ht="22.5" customHeight="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
-      <c r="C22" s="356" t="s">
+      <c r="C22" s="352" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="234"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="226"/>
       <c r="H22" s="132">
         <v>0.8</v>
       </c>
@@ -27211,13 +27209,13 @@
     <row r="23" spans="1:26" ht="45" customHeight="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
-      <c r="C23" s="356" t="s">
+      <c r="C23" s="352" t="s">
         <v>234</v>
       </c>
-      <c r="D23" s="236"/>
-      <c r="E23" s="236"/>
-      <c r="F23" s="236"/>
-      <c r="G23" s="234"/>
+      <c r="D23" s="225"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="225"/>
+      <c r="G23" s="226"/>
       <c r="H23" s="130">
         <f>0.8*H21</f>
         <v>1.3335999999999999</v>
@@ -27249,14 +27247,14 @@
     <row r="24" spans="1:26" ht="25.5" customHeight="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
-      <c r="C24" s="357" t="s">
+      <c r="C24" s="347" t="s">
         <v>236</v>
       </c>
-      <c r="D24" s="236"/>
-      <c r="E24" s="236"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="236"/>
-      <c r="H24" s="234"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="226"/>
       <c r="I24" s="134">
         <f>ROUNDUP(H23+J23,2)</f>
         <v>1.34</v>
@@ -33850,6 +33848,17 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
@@ -33858,17 +33867,6 @@
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="I11:J11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -33876,7 +33874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -34118,15 +34116,15 @@
     <row r="8" spans="1:26">
       <c r="A8" s="17"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="360" t="s">
+      <c r="C8" s="374" t="s">
         <v>239</v>
       </c>
-      <c r="D8" s="361"/>
-      <c r="E8" s="363" t="s">
+      <c r="D8" s="375"/>
+      <c r="E8" s="377" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="340"/>
-      <c r="G8" s="317"/>
+      <c r="F8" s="336"/>
+      <c r="G8" s="315"/>
       <c r="H8" s="136" t="s">
         <v>165</v>
       </c>
@@ -34136,7 +34134,7 @@
       <c r="J8" s="136" t="s">
         <v>241</v>
       </c>
-      <c r="K8" s="364" t="s">
+      <c r="K8" s="378" t="s">
         <v>242</v>
       </c>
       <c r="L8" s="17"/>
@@ -34158,8 +34156,8 @@
     <row r="9" spans="1:26" ht="30">
       <c r="A9" s="17"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="243"/>
-      <c r="D9" s="362"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="376"/>
       <c r="E9" s="137" t="s">
         <v>243</v>
       </c>
@@ -34178,7 +34176,7 @@
       <c r="J9" s="138" t="s">
         <v>225</v>
       </c>
-      <c r="K9" s="365"/>
+      <c r="K9" s="379"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
@@ -34198,14 +34196,14 @@
     <row r="10" spans="1:26" ht="19.5" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="32"/>
-      <c r="C10" s="366" t="s">
+      <c r="C10" s="380" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="317"/>
-      <c r="E10" s="367">
+      <c r="D10" s="315"/>
+      <c r="E10" s="381">
         <v>20</v>
       </c>
-      <c r="F10" s="317"/>
+      <c r="F10" s="315"/>
       <c r="G10" s="139">
         <v>10</v>
       </c>
@@ -34241,15 +34239,15 @@
     <row r="11" spans="1:26" ht="17.25" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="32"/>
-      <c r="C11" s="368" t="s">
+      <c r="C11" s="367" t="s">
         <v>248</v>
       </c>
-      <c r="D11" s="298"/>
-      <c r="E11" s="369">
+      <c r="D11" s="296"/>
+      <c r="E11" s="368">
         <f>(E10/$K10)*100</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="F11" s="298"/>
+      <c r="F11" s="296"/>
       <c r="G11" s="140">
         <f t="shared" ref="G11:J11" si="1">(G10/$K10)*100</f>
         <v>6.666666666666667</v>
@@ -34373,16 +34371,16 @@
     <row r="15" spans="1:26" ht="21">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
-      <c r="C15" s="370" t="s">
+      <c r="C15" s="369" t="s">
         <v>216</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="234"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="225"/>
+      <c r="G15" s="225"/>
+      <c r="H15" s="225"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="226"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
@@ -34403,16 +34401,16 @@
     <row r="16" spans="1:26" ht="21">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="371" t="s">
+      <c r="C16" s="370" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="236"/>
-      <c r="E16" s="236"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="234"/>
-      <c r="I16" s="372"/>
-      <c r="J16" s="240"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="226"/>
+      <c r="I16" s="371"/>
+      <c r="J16" s="228"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
@@ -34433,7 +34431,7 @@
     <row r="17" spans="1:26">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="373" t="s">
+      <c r="C17" s="372" t="s">
         <v>249</v>
       </c>
       <c r="D17" s="142"/>
@@ -34445,8 +34443,8 @@
       <c r="H17" s="146" t="s">
         <v>221</v>
       </c>
-      <c r="I17" s="243"/>
-      <c r="J17" s="244"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="232"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
@@ -34467,7 +34465,7 @@
     <row r="18" spans="1:26" ht="45.75" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="229"/>
+      <c r="C18" s="240"/>
       <c r="D18" s="147" t="s">
         <v>222</v>
       </c>
@@ -34483,8 +34481,8 @@
       <c r="H18" s="150" t="s">
         <v>225</v>
       </c>
-      <c r="I18" s="374"/>
-      <c r="J18" s="234"/>
+      <c r="I18" s="373"/>
+      <c r="J18" s="226"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
@@ -34528,8 +34526,8 @@
         <f>'CO_attainment for FA-TH ESE'!C110</f>
         <v>1</v>
       </c>
-      <c r="I19" s="375"/>
-      <c r="J19" s="309"/>
+      <c r="I19" s="363"/>
+      <c r="J19" s="307"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
@@ -34573,8 +34571,8 @@
         <f t="shared" ref="H20:H24" si="5">$H19</f>
         <v>1</v>
       </c>
-      <c r="I20" s="376"/>
-      <c r="J20" s="313"/>
+      <c r="I20" s="362"/>
+      <c r="J20" s="311"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
@@ -34618,8 +34616,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I21" s="376"/>
-      <c r="J21" s="313"/>
+      <c r="I21" s="362"/>
+      <c r="J21" s="311"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
@@ -34663,8 +34661,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I22" s="376"/>
-      <c r="J22" s="313"/>
+      <c r="I22" s="362"/>
+      <c r="J22" s="311"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
@@ -34708,8 +34706,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I23" s="376"/>
-      <c r="J23" s="313"/>
+      <c r="I23" s="362"/>
+      <c r="J23" s="311"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
@@ -34753,8 +34751,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I24" s="376"/>
-      <c r="J24" s="313"/>
+      <c r="I24" s="362"/>
+      <c r="J24" s="311"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
@@ -34798,8 +34796,8 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="I25" s="375"/>
-      <c r="J25" s="309"/>
+      <c r="I25" s="363"/>
+      <c r="J25" s="307"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
@@ -34843,8 +34841,8 @@
         <f t="shared" si="7"/>
         <v>46.666666666666664</v>
       </c>
-      <c r="I26" s="380"/>
-      <c r="J26" s="313"/>
+      <c r="I26" s="364"/>
+      <c r="J26" s="311"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
@@ -34888,8 +34886,8 @@
         <f t="shared" si="8"/>
         <v>0.46666666666666662</v>
       </c>
-      <c r="I27" s="381"/>
-      <c r="J27" s="315"/>
+      <c r="I27" s="365"/>
+      <c r="J27" s="313"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -34910,13 +34908,13 @@
     <row r="28" spans="1:26" ht="30" customHeight="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
-      <c r="C28" s="377" t="s">
+      <c r="C28" s="366" t="s">
         <v>230</v>
       </c>
-      <c r="D28" s="236"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="234"/>
+      <c r="D28" s="225"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="225"/>
+      <c r="G28" s="226"/>
       <c r="H28" s="165">
         <f>SUM(D27:H27)</f>
         <v>1.8893333333333331</v>
@@ -34943,13 +34941,13 @@
     <row r="29" spans="1:26" ht="24" customHeight="1">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="377" t="s">
+      <c r="C29" s="366" t="s">
         <v>232</v>
       </c>
-      <c r="D29" s="236"/>
-      <c r="E29" s="236"/>
-      <c r="F29" s="236"/>
-      <c r="G29" s="234"/>
+      <c r="D29" s="225"/>
+      <c r="E29" s="225"/>
+      <c r="F29" s="225"/>
+      <c r="G29" s="226"/>
       <c r="H29" s="168">
         <v>1</v>
       </c>
@@ -34975,13 +34973,13 @@
     <row r="30" spans="1:26" ht="62.25" customHeight="1">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="377" t="s">
+      <c r="C30" s="366" t="s">
         <v>234</v>
       </c>
-      <c r="D30" s="236"/>
-      <c r="E30" s="236"/>
-      <c r="F30" s="236"/>
-      <c r="G30" s="234"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="226"/>
       <c r="H30" s="165">
         <f>H29*H28</f>
         <v>1.8893333333333331</v>
@@ -35008,14 +35006,14 @@
     <row r="31" spans="1:26" ht="25.5" customHeight="1">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="378" t="s">
+      <c r="C31" s="360" t="s">
         <v>236</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="E31" s="236"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="236"/>
-      <c r="H31" s="234"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="226"/>
       <c r="I31" s="170">
         <f>H30+J30</f>
         <v>1.8893333333333331</v>
@@ -35102,11 +35100,11 @@
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
-      <c r="H34" s="230" t="s">
+      <c r="H34" s="241" t="s">
         <v>49</v>
       </c>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
+      <c r="I34" s="236"/>
+      <c r="J34" s="236"/>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
@@ -35131,11 +35129,11 @@
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
-      <c r="H35" s="379" t="s">
+      <c r="H35" s="361" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="232"/>
-      <c r="J35" s="232"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="223"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -41520,6 +41518,23 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="H34:J34"/>
     <mergeCell ref="H35:J35"/>
@@ -41530,23 +41545,6 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -41557,7 +41555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -41611,11 +41609,11 @@
       <c r="C2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="318" t="str">
+      <c r="D2" s="329" t="str">
         <f>'Overall CO attainment'!D3</f>
         <v>Programming in _C_</v>
       </c>
-      <c r="E2" s="319"/>
+      <c r="E2" s="328"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -41643,11 +41641,11 @@
       <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="318">
+      <c r="D3" s="329">
         <f>'Overall CO attainment'!D4</f>
         <v>22226</v>
       </c>
-      <c r="E3" s="319"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -41675,11 +41673,11 @@
       <c r="C4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="318" t="str">
+      <c r="D4" s="329" t="str">
         <f>'Overall CO attainment'!D5</f>
         <v>2nd SEM(CO2I SCHEME)</v>
       </c>
-      <c r="E4" s="319"/>
+      <c r="E4" s="328"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -41707,11 +41705,11 @@
       <c r="C5" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="318" t="str">
+      <c r="D5" s="329" t="str">
         <f>'Overall CO attainment'!D6</f>
         <v>2022 - 23</v>
       </c>
-      <c r="E5" s="319"/>
+      <c r="E5" s="328"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -41818,26 +41816,26 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="4"/>
-      <c r="B9" s="227" t="s">
+      <c r="B9" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="227" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="233" t="s">
+      <c r="D9" s="228"/>
+      <c r="E9" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="233" t="s">
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="234"/>
+      <c r="M9" s="226"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -41853,9 +41851,9 @@
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1">
       <c r="A10" s="4"/>
-      <c r="B10" s="228"/>
-      <c r="C10" s="241"/>
-      <c r="D10" s="242"/>
+      <c r="B10" s="239"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="230"/>
       <c r="E10" s="19" t="s">
         <v>27</v>
       </c>
@@ -41898,9 +41896,9 @@
     </row>
     <row r="11" spans="1:25" ht="119.25" customHeight="1">
       <c r="A11" s="4"/>
-      <c r="B11" s="229"/>
-      <c r="C11" s="243"/>
-      <c r="D11" s="244"/>
+      <c r="B11" s="240"/>
+      <c r="C11" s="231"/>
+      <c r="D11" s="232"/>
       <c r="E11" s="20" t="s">
         <v>36</v>
       </c>
@@ -42321,11 +42319,11 @@
     </row>
     <row r="18" spans="1:25" ht="33.75" customHeight="1">
       <c r="A18" s="4"/>
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="243" t="s">
         <v>252</v>
       </c>
-      <c r="C18" s="236"/>
-      <c r="D18" s="234"/>
+      <c r="C18" s="225"/>
+      <c r="D18" s="226"/>
       <c r="E18" s="22">
         <f t="shared" ref="E18:M18" si="0">IFERROR(AVERAGE(E12:E16),0)</f>
         <v>3</v>
@@ -42377,11 +42375,11 @@
     </row>
     <row r="19" spans="1:25" ht="28.5" customHeight="1">
       <c r="A19" s="4"/>
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="244" t="s">
         <v>253</v>
       </c>
-      <c r="C19" s="236"/>
-      <c r="D19" s="234"/>
+      <c r="C19" s="225"/>
+      <c r="D19" s="226"/>
       <c r="E19" s="173">
         <f>E18*'Overall CO attainment'!I31/3</f>
         <v>1.8893333333333331</v>
@@ -42436,8 +42434,8 @@
       <c r="B20" s="346" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="236"/>
-      <c r="D20" s="234"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="226"/>
       <c r="E20" s="108">
         <f t="shared" ref="E20:M20" si="1">ROUNDUP((E19/3)*100,2)</f>
         <v>62.98</v>
@@ -42551,12 +42549,12 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="230" t="s">
+      <c r="J23" s="241" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="225"/>
-      <c r="L23" s="225"/>
-      <c r="M23" s="225"/>
+      <c r="K23" s="236"/>
+      <c r="L23" s="236"/>
+      <c r="M23" s="236"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
@@ -42580,12 +42578,12 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="231" t="s">
+      <c r="J24" s="242" t="s">
         <v>50</v>
       </c>
-      <c r="K24" s="232"/>
-      <c r="L24" s="232"/>
-      <c r="M24" s="232"/>
+      <c r="K24" s="223"/>
+      <c r="L24" s="223"/>
+      <c r="M24" s="223"/>
       <c r="N24" s="30"/>
       <c r="O24" s="30"/>
       <c r="P24" s="4"/>
